--- a/data/raw/김포 26년/항공통계상세조회(노선) (4).xlsx
+++ b/data/raw/김포 26년/항공통계상세조회(노선) (4).xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="68">
   <si>
     <t>SEQ</t>
   </si>
@@ -38,13 +38,13 @@
     <t/>
   </si>
   <si>
-    <t>10102</t>
-  </si>
-  <si>
-    <t>1834271</t>
-  </si>
-  <si>
-    <t>17459</t>
+    <t>5056</t>
+  </si>
+  <si>
+    <t>922569</t>
+  </si>
+  <si>
+    <t>8224</t>
   </si>
   <si>
     <t>김포(GMP)</t>
@@ -53,175 +53,169 @@
     <t>간사이(KIX)</t>
   </si>
   <si>
-    <t>600</t>
-  </si>
-  <si>
-    <t>104186</t>
-  </si>
-  <si>
-    <t>1317</t>
+    <t>300</t>
+  </si>
+  <si>
+    <t>50610</t>
+  </si>
+  <si>
+    <t>701</t>
   </si>
   <si>
     <t>광주(KWJ)</t>
   </si>
   <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>6847</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>김해(PUS)</t>
+  </si>
+  <si>
+    <t>577</t>
+  </si>
+  <si>
+    <t>87613</t>
+  </si>
+  <si>
+    <t>355</t>
+  </si>
+  <si>
+    <t>나고야(NGO)</t>
+  </si>
+  <si>
+    <t>8905</t>
+  </si>
+  <si>
+    <t>91</t>
+  </si>
+  <si>
+    <t>다싱(PKX)</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>5227</t>
+  </si>
+  <si>
+    <t>95</t>
+  </si>
+  <si>
+    <t>도쿄 하네다(HND)</t>
+  </si>
+  <si>
+    <t>360</t>
+  </si>
+  <si>
+    <t>86475</t>
+  </si>
+  <si>
+    <t>1971</t>
+  </si>
+  <si>
+    <t>북경(PEK)</t>
+  </si>
+  <si>
+    <t>89</t>
+  </si>
+  <si>
+    <t>14524</t>
+  </si>
+  <si>
+    <t>183</t>
+  </si>
+  <si>
+    <t>사천(HIN)</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>3017</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>쑹산(TSA)</t>
+  </si>
+  <si>
+    <t>10421</t>
+  </si>
+  <si>
+    <t>143</t>
+  </si>
+  <si>
+    <t>여수(RSU)</t>
+  </si>
+  <si>
+    <t>87</t>
+  </si>
+  <si>
+    <t>10037</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>울산(USN)</t>
+  </si>
+  <si>
+    <t>72</t>
+  </si>
+  <si>
+    <t>8687</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>제주(CJU)</t>
+  </si>
+  <si>
+    <t>3138</t>
+  </si>
+  <si>
+    <t>589609</t>
+  </si>
+  <si>
+    <t>4144</t>
+  </si>
+  <si>
+    <t>카오슝(KHH)</t>
+  </si>
+  <si>
+    <t>47</t>
+  </si>
+  <si>
+    <t>7621</t>
+  </si>
+  <si>
+    <t>포항 경주(KPO)</t>
+  </si>
+  <si>
+    <t>1856</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>홍차오(SHA)</t>
+  </si>
+  <si>
     <t>120</t>
   </si>
   <si>
-    <t>14136</t>
-  </si>
-  <si>
-    <t>37</t>
-  </si>
-  <si>
-    <t>김해(PUS)</t>
-  </si>
-  <si>
-    <t>1174</t>
-  </si>
-  <si>
-    <t>177127</t>
-  </si>
-  <si>
-    <t>741</t>
-  </si>
-  <si>
-    <t>나고야(NGO)</t>
-  </si>
-  <si>
-    <t>17813</t>
-  </si>
-  <si>
-    <t>160</t>
-  </si>
-  <si>
-    <t>다싱(PKX)</t>
-  </si>
-  <si>
-    <t>60</t>
-  </si>
-  <si>
-    <t>10587</t>
-  </si>
-  <si>
-    <t>150</t>
-  </si>
-  <si>
-    <t>도쿄 하네다(HND)</t>
-  </si>
-  <si>
-    <t>720</t>
-  </si>
-  <si>
-    <t>172399</t>
-  </si>
-  <si>
-    <t>3107</t>
-  </si>
-  <si>
-    <t>북경(PEK)</t>
-  </si>
-  <si>
-    <t>178</t>
-  </si>
-  <si>
-    <t>29204</t>
-  </si>
-  <si>
-    <t>346</t>
-  </si>
-  <si>
-    <t>사천(HIN)</t>
-  </si>
-  <si>
-    <t>56</t>
-  </si>
-  <si>
-    <t>6178</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>쑹산(TSA)</t>
-  </si>
-  <si>
-    <t>20359</t>
-  </si>
-  <si>
-    <t>254</t>
-  </si>
-  <si>
-    <t>여수(RSU)</t>
-  </si>
-  <si>
-    <t>174</t>
-  </si>
-  <si>
-    <t>20857</t>
-  </si>
-  <si>
-    <t>67</t>
-  </si>
-  <si>
-    <t>울산(USN)</t>
-  </si>
-  <si>
-    <t>144</t>
-  </si>
-  <si>
-    <t>17426</t>
-  </si>
-  <si>
-    <t>53</t>
-  </si>
-  <si>
-    <t>제주(CJU)</t>
-  </si>
-  <si>
-    <t>6245</t>
-  </si>
-  <si>
-    <t>1161191</t>
-  </si>
-  <si>
-    <t>9589</t>
-  </si>
-  <si>
-    <t>카오슝(KHH)</t>
-  </si>
-  <si>
-    <t>94</t>
-  </si>
-  <si>
-    <t>15306</t>
-  </si>
-  <si>
-    <t>167</t>
-  </si>
-  <si>
-    <t>포항 경주(KPO)</t>
-  </si>
-  <si>
-    <t>57</t>
-  </si>
-  <si>
-    <t>3911</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>홍차오(SHA)</t>
-  </si>
-  <si>
-    <t>240</t>
-  </si>
-  <si>
-    <t>63591</t>
-  </si>
-  <si>
-    <t>1451</t>
+    <t>31120</t>
+  </si>
+  <si>
+    <t>361</t>
   </si>
 </sst>
 </file>
@@ -572,7 +566,7 @@
         <v>60</v>
       </c>
       <c r="F15" t="s" s="0">
-        <v>61</v>
+        <v>26</v>
       </c>
     </row>
     <row r="16">
@@ -583,16 +577,16 @@
         <v>11</v>
       </c>
       <c r="C16" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="D16" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="E16" t="s" s="0">
         <v>62</v>
       </c>
-      <c r="D16" t="s" s="0">
+      <c r="F16" t="s" s="0">
         <v>63</v>
-      </c>
-      <c r="E16" t="s" s="0">
-        <v>64</v>
-      </c>
-      <c r="F16" t="s" s="0">
-        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -603,16 +597,16 @@
         <v>11</v>
       </c>
       <c r="C17" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="D17" t="s" s="0">
+        <v>65</v>
+      </c>
+      <c r="E17" t="s" s="0">
         <v>66</v>
       </c>
-      <c r="D17" t="s" s="0">
+      <c r="F17" t="s" s="0">
         <v>67</v>
-      </c>
-      <c r="E17" t="s" s="0">
-        <v>68</v>
-      </c>
-      <c r="F17" t="s" s="0">
-        <v>69</v>
       </c>
     </row>
   </sheetData>
